--- a/ExcelFiles/age and time calculation.xlsx
+++ b/ExcelFiles/age and time calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Excel_Github\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107C8501-570F-4DAC-93C9-E7AC6BECB4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0308150-DC7A-40F5-AAB4-17AD894AFAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9150" yWindow="1905" windowWidth="15045" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9150" yWindow="1905" windowWidth="15045" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Age" sheetId="1" r:id="rId1"/>
